--- a/02-governance/Control Objectives Register.xlsx
+++ b/02-governance/Control Objectives Register.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e73e59fca4c100b3/Documents/NexaCore IAM/02-governance/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{2E737FDA-0B9B-4436-817A-4DD884ED8325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2871F233-2D6C-45C8-8078-01D05C6428C9}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{2E737FDA-0B9B-4436-817A-4DD884ED8325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58F04FD6-F2BE-4F7D-B55E-1AD7D6B45CAE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F639C803-F065-4EA7-92BB-A2EAEE744DC2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="89">
   <si>
     <t>Control ID</t>
   </si>
@@ -243,6 +243,66 @@
   </si>
   <si>
     <t>NexaCore</t>
+  </si>
+  <si>
+    <t>IAM-13</t>
+  </si>
+  <si>
+    <t>Access matches the defined Role-Permission Matrix</t>
+  </si>
+  <si>
+    <t>Excessive/inappropriate access</t>
+  </si>
+  <si>
+    <t>Role membership vs. matrix comparison</t>
+  </si>
+  <si>
+    <t>IAM-14</t>
+  </si>
+  <si>
+    <t>SoD conflicts are identified and have a compensating control or accepted risk</t>
+  </si>
+  <si>
+    <t>Fraud/error not independently caught</t>
+  </si>
+  <si>
+    <t>SoD matrix + compensating control evidence</t>
+  </si>
+  <si>
+    <t>IAM-15</t>
+  </si>
+  <si>
+    <t>Privileged access is approved, time-appropriate, and monitored</t>
+  </si>
+  <si>
+    <t>High-impact unauthorized activity</t>
+  </si>
+  <si>
+    <t>Privileged access register + monitoring evidence</t>
+  </si>
+  <si>
+    <t>IAM-16</t>
+  </si>
+  <si>
+    <t>Service accounts have a named owner and defined review cycle</t>
+  </si>
+  <si>
+    <t>Orphaned/unmanaged service accounts</t>
+  </si>
+  <si>
+    <t>Service account register</t>
+  </si>
+  <si>
+    <t>IAM-17</t>
+  </si>
+  <si>
+    <t>MFA is enforced, with all exceptions documented and approved</t>
+  </si>
+  <si>
+    <t>Authentication compromise</t>
+  </si>
+  <si>
+    <t>MFA coverage report + exception log</t>
   </si>
 </sst>
 </file>
@@ -309,7 +369,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -319,6 +379,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -657,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8604DC43-6E87-427D-A136-BC33744AFD21}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -938,6 +999,86 @@
         <v>67</v>
       </c>
     </row>
+    <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="5"/>
+    </row>
+    <row r="17" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F20" s="5"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="147" orientation="portrait" r:id="rId1"/>
